--- a/Pemindah JD adaptif V6/TemplateJobDescBaruKosongan/Template GOL 5_Managerial.xlsx
+++ b/Pemindah JD adaptif V6/TemplateJobDescBaruKosongan/Template GOL 5_Managerial.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\titipan Feli\PROYEK GEDE\Database\Template Baru kosong - Cloud\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\z\TemplateJobDescBaruKosongan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{852DE38A-ACB0-46D6-9DBB-55082CFBD06B}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29916DE0-0419-450C-B998-8FAFC155603B}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" xr2:uid="{B4CA32BC-DA9F-4539-8D41-F96D4CBDAEFA}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="69">
   <si>
     <t>JOB DESCRIPTION</t>
   </si>
@@ -120,9 +120,6 @@
     <t>Menjalin informasi dan komunikasi dengan internal departemen</t>
   </si>
   <si>
-    <t>Berhubungan dengan seluruh departemen PT UBS perihal :</t>
-  </si>
-  <si>
     <t>Berhubungan dengan pihak eksternal dengan batasan perihal :</t>
   </si>
   <si>
@@ -190,9 +187,6 @@
   </si>
   <si>
     <t xml:space="preserve">Melakukan genba secara rutin untuk memastikan efektifitas dan konsistensi : </t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <r>
@@ -255,16 +249,13 @@
     <t xml:space="preserve">Memahami alur proses keseluruhan departemen </t>
   </si>
   <si>
-    <t>1.</t>
-  </si>
-  <si>
     <t>ExternalXYZConnection</t>
   </si>
   <si>
-    <t>2.</t>
-  </si>
-  <si>
-    <t>3.</t>
+    <t>ExternalConnection</t>
+  </si>
+  <si>
+    <t>Berhubungan dengan seluruh departemen PT XYZ perihal :</t>
   </si>
 </sst>
 </file>
@@ -633,7 +624,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1060,6 +1051,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1069,6 +1063,63 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1085,63 +1136,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1221,6 +1215,54 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="AutoShape 1" descr="Cute Bear Vector Sticker, Bear Clipart, Cute Clipart ...">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93393D52-AFCE-45B9-8FCB-9C7351D5F229}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="742950" y="381000"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1623,37 +1665,37 @@
       <c r="J2" s="50"/>
       <c r="K2" s="50"/>
       <c r="L2" s="51"/>
-      <c r="M2" s="168" t="s">
+      <c r="M2" s="163" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="169"/>
-      <c r="O2" s="169"/>
-      <c r="P2" s="169"/>
-      <c r="Q2" s="169"/>
-      <c r="R2" s="169"/>
-      <c r="S2" s="169"/>
-      <c r="T2" s="169"/>
-      <c r="U2" s="169"/>
-      <c r="V2" s="169"/>
-      <c r="W2" s="169"/>
-      <c r="X2" s="169"/>
-      <c r="Y2" s="169"/>
-      <c r="Z2" s="169"/>
-      <c r="AA2" s="169"/>
-      <c r="AB2" s="169"/>
-      <c r="AC2" s="169"/>
-      <c r="AD2" s="169"/>
-      <c r="AE2" s="169"/>
-      <c r="AF2" s="169"/>
-      <c r="AG2" s="169"/>
-      <c r="AH2" s="169"/>
-      <c r="AI2" s="169"/>
-      <c r="AJ2" s="169"/>
-      <c r="AK2" s="169"/>
-      <c r="AL2" s="169"/>
-      <c r="AM2" s="169"/>
-      <c r="AN2" s="169"/>
-      <c r="AO2" s="170"/>
+      <c r="N2" s="164"/>
+      <c r="O2" s="164"/>
+      <c r="P2" s="164"/>
+      <c r="Q2" s="164"/>
+      <c r="R2" s="164"/>
+      <c r="S2" s="164"/>
+      <c r="T2" s="164"/>
+      <c r="U2" s="164"/>
+      <c r="V2" s="164"/>
+      <c r="W2" s="164"/>
+      <c r="X2" s="164"/>
+      <c r="Y2" s="164"/>
+      <c r="Z2" s="164"/>
+      <c r="AA2" s="164"/>
+      <c r="AB2" s="164"/>
+      <c r="AC2" s="164"/>
+      <c r="AD2" s="164"/>
+      <c r="AE2" s="164"/>
+      <c r="AF2" s="164"/>
+      <c r="AG2" s="164"/>
+      <c r="AH2" s="164"/>
+      <c r="AI2" s="164"/>
+      <c r="AJ2" s="164"/>
+      <c r="AK2" s="164"/>
+      <c r="AL2" s="164"/>
+      <c r="AM2" s="164"/>
+      <c r="AN2" s="164"/>
+      <c r="AO2" s="165"/>
       <c r="AP2" s="120"/>
       <c r="AQ2" s="52" t="s">
         <v>1</v>
@@ -1666,7 +1708,7 @@
         <v>2</v>
       </c>
       <c r="AW2" s="121" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AX2" s="52"/>
       <c r="AY2" s="52"/>
@@ -1686,36 +1728,37 @@
     </row>
     <row r="3" spans="2:68" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="31"/>
+      <c r="E3"/>
       <c r="L3" s="17"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="172"/>
-      <c r="O3" s="172"/>
-      <c r="P3" s="172"/>
-      <c r="Q3" s="172"/>
-      <c r="R3" s="172"/>
-      <c r="S3" s="172"/>
-      <c r="T3" s="172"/>
-      <c r="U3" s="172"/>
-      <c r="V3" s="172"/>
-      <c r="W3" s="172"/>
-      <c r="X3" s="172"/>
-      <c r="Y3" s="172"/>
-      <c r="Z3" s="172"/>
-      <c r="AA3" s="172"/>
-      <c r="AB3" s="172"/>
-      <c r="AC3" s="172"/>
-      <c r="AD3" s="172"/>
-      <c r="AE3" s="172"/>
-      <c r="AF3" s="172"/>
-      <c r="AG3" s="172"/>
-      <c r="AH3" s="172"/>
-      <c r="AI3" s="172"/>
-      <c r="AJ3" s="172"/>
-      <c r="AK3" s="172"/>
-      <c r="AL3" s="172"/>
-      <c r="AM3" s="172"/>
-      <c r="AN3" s="172"/>
-      <c r="AO3" s="173"/>
+      <c r="M3" s="166"/>
+      <c r="N3" s="167"/>
+      <c r="O3" s="167"/>
+      <c r="P3" s="167"/>
+      <c r="Q3" s="167"/>
+      <c r="R3" s="167"/>
+      <c r="S3" s="167"/>
+      <c r="T3" s="167"/>
+      <c r="U3" s="167"/>
+      <c r="V3" s="167"/>
+      <c r="W3" s="167"/>
+      <c r="X3" s="167"/>
+      <c r="Y3" s="167"/>
+      <c r="Z3" s="167"/>
+      <c r="AA3" s="167"/>
+      <c r="AB3" s="167"/>
+      <c r="AC3" s="167"/>
+      <c r="AD3" s="167"/>
+      <c r="AE3" s="167"/>
+      <c r="AF3" s="167"/>
+      <c r="AG3" s="167"/>
+      <c r="AH3" s="167"/>
+      <c r="AI3" s="167"/>
+      <c r="AJ3" s="167"/>
+      <c r="AK3" s="167"/>
+      <c r="AL3" s="167"/>
+      <c r="AM3" s="167"/>
+      <c r="AN3" s="167"/>
+      <c r="AO3" s="168"/>
       <c r="AP3" s="122"/>
       <c r="AQ3" s="55"/>
       <c r="AR3" s="55"/>
@@ -1742,35 +1785,35 @@
     <row r="4" spans="2:68" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="31"/>
       <c r="L4" s="17"/>
-      <c r="M4" s="171"/>
-      <c r="N4" s="172"/>
-      <c r="O4" s="172"/>
-      <c r="P4" s="172"/>
-      <c r="Q4" s="172"/>
-      <c r="R4" s="172"/>
-      <c r="S4" s="172"/>
-      <c r="T4" s="172"/>
-      <c r="U4" s="172"/>
-      <c r="V4" s="172"/>
-      <c r="W4" s="172"/>
-      <c r="X4" s="172"/>
-      <c r="Y4" s="172"/>
-      <c r="Z4" s="172"/>
-      <c r="AA4" s="172"/>
-      <c r="AB4" s="172"/>
-      <c r="AC4" s="172"/>
-      <c r="AD4" s="172"/>
-      <c r="AE4" s="172"/>
-      <c r="AF4" s="172"/>
-      <c r="AG4" s="172"/>
-      <c r="AH4" s="172"/>
-      <c r="AI4" s="172"/>
-      <c r="AJ4" s="172"/>
-      <c r="AK4" s="172"/>
-      <c r="AL4" s="172"/>
-      <c r="AM4" s="172"/>
-      <c r="AN4" s="172"/>
-      <c r="AO4" s="173"/>
+      <c r="M4" s="166"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="167"/>
+      <c r="P4" s="167"/>
+      <c r="Q4" s="167"/>
+      <c r="R4" s="167"/>
+      <c r="S4" s="167"/>
+      <c r="T4" s="167"/>
+      <c r="U4" s="167"/>
+      <c r="V4" s="167"/>
+      <c r="W4" s="167"/>
+      <c r="X4" s="167"/>
+      <c r="Y4" s="167"/>
+      <c r="Z4" s="167"/>
+      <c r="AA4" s="167"/>
+      <c r="AB4" s="167"/>
+      <c r="AC4" s="167"/>
+      <c r="AD4" s="167"/>
+      <c r="AE4" s="167"/>
+      <c r="AF4" s="167"/>
+      <c r="AG4" s="167"/>
+      <c r="AH4" s="167"/>
+      <c r="AI4" s="167"/>
+      <c r="AJ4" s="167"/>
+      <c r="AK4" s="167"/>
+      <c r="AL4" s="167"/>
+      <c r="AM4" s="167"/>
+      <c r="AN4" s="167"/>
+      <c r="AO4" s="168"/>
       <c r="AP4" s="122"/>
       <c r="AQ4" s="55" t="s">
         <v>3</v>
@@ -1783,7 +1826,7 @@
         <v>2</v>
       </c>
       <c r="AW4" s="123" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AX4" s="55"/>
       <c r="AY4" s="55"/>
@@ -1813,35 +1856,35 @@
       <c r="J5" s="28"/>
       <c r="K5" s="28"/>
       <c r="L5" s="36"/>
-      <c r="M5" s="174"/>
-      <c r="N5" s="175"/>
-      <c r="O5" s="175"/>
-      <c r="P5" s="175"/>
-      <c r="Q5" s="175"/>
-      <c r="R5" s="175"/>
-      <c r="S5" s="175"/>
-      <c r="T5" s="175"/>
-      <c r="U5" s="175"/>
-      <c r="V5" s="175"/>
-      <c r="W5" s="175"/>
-      <c r="X5" s="175"/>
-      <c r="Y5" s="175"/>
-      <c r="Z5" s="175"/>
-      <c r="AA5" s="175"/>
-      <c r="AB5" s="175"/>
-      <c r="AC5" s="175"/>
-      <c r="AD5" s="175"/>
-      <c r="AE5" s="175"/>
-      <c r="AF5" s="175"/>
-      <c r="AG5" s="175"/>
-      <c r="AH5" s="175"/>
-      <c r="AI5" s="175"/>
-      <c r="AJ5" s="175"/>
-      <c r="AK5" s="175"/>
-      <c r="AL5" s="175"/>
-      <c r="AM5" s="175"/>
-      <c r="AN5" s="175"/>
-      <c r="AO5" s="176"/>
+      <c r="M5" s="169"/>
+      <c r="N5" s="170"/>
+      <c r="O5" s="170"/>
+      <c r="P5" s="170"/>
+      <c r="Q5" s="170"/>
+      <c r="R5" s="170"/>
+      <c r="S5" s="170"/>
+      <c r="T5" s="170"/>
+      <c r="U5" s="170"/>
+      <c r="V5" s="170"/>
+      <c r="W5" s="170"/>
+      <c r="X5" s="170"/>
+      <c r="Y5" s="170"/>
+      <c r="Z5" s="170"/>
+      <c r="AA5" s="170"/>
+      <c r="AB5" s="170"/>
+      <c r="AC5" s="170"/>
+      <c r="AD5" s="170"/>
+      <c r="AE5" s="170"/>
+      <c r="AF5" s="170"/>
+      <c r="AG5" s="170"/>
+      <c r="AH5" s="170"/>
+      <c r="AI5" s="170"/>
+      <c r="AJ5" s="170"/>
+      <c r="AK5" s="170"/>
+      <c r="AL5" s="170"/>
+      <c r="AM5" s="170"/>
+      <c r="AN5" s="170"/>
+      <c r="AO5" s="171"/>
       <c r="AP5" s="124"/>
       <c r="AQ5" s="58" t="s">
         <v>4</v>
@@ -1854,7 +1897,7 @@
         <v>2</v>
       </c>
       <c r="AW5" s="28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AX5" s="58"/>
       <c r="AY5" s="58"/>
@@ -2004,99 +2047,99 @@
       <c r="BP7" s="9"/>
     </row>
     <row r="8" spans="2:68" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="150" t="s">
+      <c r="B8" s="151" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="151"/>
-      <c r="D8" s="151"/>
-      <c r="E8" s="151"/>
-      <c r="F8" s="151"/>
-      <c r="G8" s="151"/>
-      <c r="H8" s="151"/>
-      <c r="I8" s="151"/>
-      <c r="J8" s="151"/>
-      <c r="K8" s="151"/>
-      <c r="L8" s="151"/>
-      <c r="M8" s="151"/>
-      <c r="N8" s="151"/>
-      <c r="O8" s="151"/>
-      <c r="P8" s="151"/>
-      <c r="Q8" s="151"/>
-      <c r="R8" s="151"/>
-      <c r="S8" s="151"/>
-      <c r="T8" s="151"/>
-      <c r="U8" s="151"/>
-      <c r="V8" s="151"/>
-      <c r="W8" s="152"/>
-      <c r="X8" s="150" t="s">
+      <c r="C8" s="152"/>
+      <c r="D8" s="152"/>
+      <c r="E8" s="152"/>
+      <c r="F8" s="152"/>
+      <c r="G8" s="152"/>
+      <c r="H8" s="152"/>
+      <c r="I8" s="152"/>
+      <c r="J8" s="152"/>
+      <c r="K8" s="152"/>
+      <c r="L8" s="152"/>
+      <c r="M8" s="152"/>
+      <c r="N8" s="152"/>
+      <c r="O8" s="152"/>
+      <c r="P8" s="152"/>
+      <c r="Q8" s="152"/>
+      <c r="R8" s="152"/>
+      <c r="S8" s="152"/>
+      <c r="T8" s="152"/>
+      <c r="U8" s="152"/>
+      <c r="V8" s="152"/>
+      <c r="W8" s="153"/>
+      <c r="X8" s="151" t="s">
         <v>6</v>
       </c>
-      <c r="Y8" s="151"/>
-      <c r="Z8" s="151"/>
-      <c r="AA8" s="151"/>
-      <c r="AB8" s="151"/>
-      <c r="AC8" s="151"/>
-      <c r="AD8" s="151"/>
-      <c r="AE8" s="151"/>
-      <c r="AF8" s="151"/>
-      <c r="AG8" s="151"/>
-      <c r="AH8" s="151"/>
-      <c r="AI8" s="151"/>
-      <c r="AJ8" s="151"/>
-      <c r="AK8" s="151"/>
-      <c r="AL8" s="151"/>
-      <c r="AM8" s="151"/>
-      <c r="AN8" s="151"/>
-      <c r="AO8" s="152"/>
+      <c r="Y8" s="152"/>
+      <c r="Z8" s="152"/>
+      <c r="AA8" s="152"/>
+      <c r="AB8" s="152"/>
+      <c r="AC8" s="152"/>
+      <c r="AD8" s="152"/>
+      <c r="AE8" s="152"/>
+      <c r="AF8" s="152"/>
+      <c r="AG8" s="152"/>
+      <c r="AH8" s="152"/>
+      <c r="AI8" s="152"/>
+      <c r="AJ8" s="152"/>
+      <c r="AK8" s="152"/>
+      <c r="AL8" s="152"/>
+      <c r="AM8" s="152"/>
+      <c r="AN8" s="152"/>
+      <c r="AO8" s="153"/>
       <c r="AP8" s="69"/>
-      <c r="AQ8" s="150" t="s">
+      <c r="AQ8" s="151" t="s">
         <v>7</v>
       </c>
-      <c r="AR8" s="151"/>
-      <c r="AS8" s="151"/>
-      <c r="AT8" s="151"/>
-      <c r="AU8" s="151"/>
-      <c r="AV8" s="151"/>
-      <c r="AW8" s="151"/>
-      <c r="AX8" s="151"/>
-      <c r="AY8" s="151"/>
-      <c r="AZ8" s="151"/>
-      <c r="BA8" s="151"/>
-      <c r="BB8" s="151"/>
-      <c r="BC8" s="151"/>
-      <c r="BD8" s="151"/>
-      <c r="BE8" s="151"/>
-      <c r="BF8" s="151"/>
-      <c r="BG8" s="151"/>
-      <c r="BH8" s="151"/>
-      <c r="BI8" s="151"/>
-      <c r="BJ8" s="151"/>
-      <c r="BK8" s="152"/>
+      <c r="AR8" s="152"/>
+      <c r="AS8" s="152"/>
+      <c r="AT8" s="152"/>
+      <c r="AU8" s="152"/>
+      <c r="AV8" s="152"/>
+      <c r="AW8" s="152"/>
+      <c r="AX8" s="152"/>
+      <c r="AY8" s="152"/>
+      <c r="AZ8" s="152"/>
+      <c r="BA8" s="152"/>
+      <c r="BB8" s="152"/>
+      <c r="BC8" s="152"/>
+      <c r="BD8" s="152"/>
+      <c r="BE8" s="152"/>
+      <c r="BF8" s="152"/>
+      <c r="BG8" s="152"/>
+      <c r="BH8" s="152"/>
+      <c r="BI8" s="152"/>
+      <c r="BJ8" s="152"/>
+      <c r="BK8" s="153"/>
       <c r="BL8" s="30"/>
       <c r="BN8" s="9"/>
     </row>
     <row r="9" spans="2:68" ht="16.7" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B9" s="31"/>
-      <c r="X9" s="159" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y9" s="160"/>
-      <c r="Z9" s="160"/>
-      <c r="AA9" s="160"/>
-      <c r="AB9" s="160"/>
-      <c r="AC9" s="160"/>
-      <c r="AD9" s="160"/>
-      <c r="AE9" s="160"/>
-      <c r="AF9" s="160"/>
-      <c r="AG9" s="160"/>
-      <c r="AH9" s="160"/>
-      <c r="AI9" s="160"/>
-      <c r="AJ9" s="160"/>
-      <c r="AK9" s="160"/>
-      <c r="AL9" s="160"/>
-      <c r="AM9" s="160"/>
-      <c r="AN9" s="160"/>
-      <c r="AO9" s="161"/>
+      <c r="X9" s="154" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y9" s="155"/>
+      <c r="Z9" s="155"/>
+      <c r="AA9" s="155"/>
+      <c r="AB9" s="155"/>
+      <c r="AC9" s="155"/>
+      <c r="AD9" s="155"/>
+      <c r="AE9" s="155"/>
+      <c r="AF9" s="155"/>
+      <c r="AG9" s="155"/>
+      <c r="AH9" s="155"/>
+      <c r="AI9" s="155"/>
+      <c r="AJ9" s="155"/>
+      <c r="AK9" s="155"/>
+      <c r="AL9" s="155"/>
+      <c r="AM9" s="155"/>
+      <c r="AN9" s="155"/>
+      <c r="AO9" s="156"/>
       <c r="AP9" s="31"/>
       <c r="AQ9" s="29" t="s">
         <v>8</v>
@@ -2107,24 +2150,24 @@
     </row>
     <row r="10" spans="2:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="31"/>
-      <c r="X10" s="162"/>
-      <c r="Y10" s="163"/>
-      <c r="Z10" s="163"/>
-      <c r="AA10" s="163"/>
-      <c r="AB10" s="163"/>
-      <c r="AC10" s="163"/>
-      <c r="AD10" s="163"/>
-      <c r="AE10" s="163"/>
-      <c r="AF10" s="163"/>
-      <c r="AG10" s="163"/>
-      <c r="AH10" s="163"/>
-      <c r="AI10" s="163"/>
-      <c r="AJ10" s="163"/>
-      <c r="AK10" s="163"/>
-      <c r="AL10" s="163"/>
-      <c r="AM10" s="163"/>
-      <c r="AN10" s="163"/>
-      <c r="AO10" s="164"/>
+      <c r="X10" s="157"/>
+      <c r="Y10" s="158"/>
+      <c r="Z10" s="158"/>
+      <c r="AA10" s="158"/>
+      <c r="AB10" s="158"/>
+      <c r="AC10" s="158"/>
+      <c r="AD10" s="158"/>
+      <c r="AE10" s="158"/>
+      <c r="AF10" s="158"/>
+      <c r="AG10" s="158"/>
+      <c r="AH10" s="158"/>
+      <c r="AI10" s="158"/>
+      <c r="AJ10" s="158"/>
+      <c r="AK10" s="158"/>
+      <c r="AL10" s="158"/>
+      <c r="AM10" s="158"/>
+      <c r="AN10" s="158"/>
+      <c r="AO10" s="159"/>
       <c r="AP10" s="70"/>
       <c r="AQ10" s="3"/>
       <c r="AR10" s="4"/>
@@ -2134,24 +2177,24 @@
     <row r="11" spans="2:68" ht="16.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="31"/>
       <c r="W11" s="17"/>
-      <c r="X11" s="165"/>
-      <c r="Y11" s="166"/>
-      <c r="Z11" s="166"/>
-      <c r="AA11" s="166"/>
-      <c r="AB11" s="166"/>
-      <c r="AC11" s="166"/>
-      <c r="AD11" s="166"/>
-      <c r="AE11" s="166"/>
-      <c r="AF11" s="166"/>
-      <c r="AG11" s="166"/>
-      <c r="AH11" s="166"/>
-      <c r="AI11" s="166"/>
-      <c r="AJ11" s="166"/>
-      <c r="AK11" s="166"/>
-      <c r="AL11" s="166"/>
-      <c r="AM11" s="166"/>
-      <c r="AN11" s="166"/>
-      <c r="AO11" s="167"/>
+      <c r="X11" s="160"/>
+      <c r="Y11" s="161"/>
+      <c r="Z11" s="161"/>
+      <c r="AA11" s="161"/>
+      <c r="AB11" s="161"/>
+      <c r="AC11" s="161"/>
+      <c r="AD11" s="161"/>
+      <c r="AE11" s="161"/>
+      <c r="AF11" s="161"/>
+      <c r="AG11" s="161"/>
+      <c r="AH11" s="161"/>
+      <c r="AI11" s="161"/>
+      <c r="AJ11" s="161"/>
+      <c r="AK11" s="161"/>
+      <c r="AL11" s="161"/>
+      <c r="AM11" s="161"/>
+      <c r="AN11" s="161"/>
+      <c r="AO11" s="162"/>
       <c r="AP11" s="70"/>
       <c r="AQ11" s="5"/>
       <c r="BK11" s="17"/>
@@ -2160,26 +2203,26 @@
     <row r="12" spans="2:68" ht="16.7" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="31"/>
       <c r="W12" s="17"/>
-      <c r="X12" s="150" t="s">
+      <c r="X12" s="151" t="s">
         <v>9</v>
       </c>
-      <c r="Y12" s="151"/>
-      <c r="Z12" s="151"/>
-      <c r="AA12" s="151"/>
-      <c r="AB12" s="151"/>
-      <c r="AC12" s="151"/>
-      <c r="AD12" s="151"/>
-      <c r="AE12" s="151"/>
-      <c r="AF12" s="151"/>
-      <c r="AG12" s="151"/>
-      <c r="AH12" s="151"/>
-      <c r="AI12" s="151"/>
-      <c r="AJ12" s="151"/>
-      <c r="AK12" s="151"/>
-      <c r="AL12" s="151"/>
-      <c r="AM12" s="151"/>
-      <c r="AN12" s="151"/>
-      <c r="AO12" s="152"/>
+      <c r="Y12" s="152"/>
+      <c r="Z12" s="152"/>
+      <c r="AA12" s="152"/>
+      <c r="AB12" s="152"/>
+      <c r="AC12" s="152"/>
+      <c r="AD12" s="152"/>
+      <c r="AE12" s="152"/>
+      <c r="AF12" s="152"/>
+      <c r="AG12" s="152"/>
+      <c r="AH12" s="152"/>
+      <c r="AI12" s="152"/>
+      <c r="AJ12" s="152"/>
+      <c r="AK12" s="152"/>
+      <c r="AL12" s="152"/>
+      <c r="AM12" s="152"/>
+      <c r="AN12" s="152"/>
+      <c r="AO12" s="153"/>
       <c r="AP12" s="70"/>
       <c r="AQ12" s="30" t="s">
         <v>10</v>
@@ -2254,7 +2297,7 @@
       <c r="AO15" s="9"/>
       <c r="AP15" s="70"/>
       <c r="AQ15" s="30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AR15" s="9"/>
       <c r="AS15" s="9"/>
@@ -2428,14 +2471,14 @@
       <c r="K22" s="28"/>
       <c r="L22" s="28"/>
       <c r="M22" s="28" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N22" s="28"/>
       <c r="O22" s="28"/>
       <c r="P22" s="28"/>
       <c r="Q22" s="28"/>
       <c r="R22" s="28" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="S22" s="28"/>
       <c r="T22" s="28"/>
@@ -2485,70 +2528,70 @@
       <c r="BN22" s="9"/>
     </row>
     <row r="23" spans="2:68" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="150" t="s">
+      <c r="B23" s="151" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="151"/>
-      <c r="D23" s="151"/>
-      <c r="E23" s="151"/>
-      <c r="F23" s="151"/>
-      <c r="G23" s="151"/>
-      <c r="H23" s="151"/>
-      <c r="I23" s="151"/>
-      <c r="J23" s="151"/>
-      <c r="K23" s="151"/>
-      <c r="L23" s="151"/>
-      <c r="M23" s="151"/>
-      <c r="N23" s="151"/>
-      <c r="O23" s="151"/>
-      <c r="P23" s="151"/>
-      <c r="Q23" s="151"/>
-      <c r="R23" s="151"/>
-      <c r="S23" s="151"/>
-      <c r="T23" s="151"/>
-      <c r="U23" s="151"/>
-      <c r="V23" s="151"/>
-      <c r="W23" s="151"/>
-      <c r="X23" s="151"/>
-      <c r="Y23" s="151"/>
-      <c r="Z23" s="151"/>
-      <c r="AA23" s="151"/>
-      <c r="AB23" s="151"/>
-      <c r="AC23" s="151"/>
-      <c r="AD23" s="151"/>
-      <c r="AE23" s="151"/>
-      <c r="AF23" s="151"/>
-      <c r="AG23" s="151"/>
-      <c r="AH23" s="151"/>
-      <c r="AI23" s="151"/>
-      <c r="AJ23" s="151"/>
-      <c r="AK23" s="151"/>
-      <c r="AL23" s="151"/>
-      <c r="AM23" s="151"/>
-      <c r="AN23" s="151"/>
-      <c r="AO23" s="151"/>
-      <c r="AP23" s="151"/>
-      <c r="AQ23" s="151"/>
-      <c r="AR23" s="151"/>
-      <c r="AS23" s="151"/>
-      <c r="AT23" s="151"/>
-      <c r="AU23" s="151"/>
-      <c r="AV23" s="151"/>
-      <c r="AW23" s="151"/>
-      <c r="AX23" s="151"/>
-      <c r="AY23" s="151"/>
-      <c r="AZ23" s="151"/>
-      <c r="BA23" s="151"/>
-      <c r="BB23" s="151"/>
-      <c r="BC23" s="151"/>
-      <c r="BD23" s="151"/>
-      <c r="BE23" s="151"/>
-      <c r="BF23" s="151"/>
-      <c r="BG23" s="151"/>
-      <c r="BH23" s="151"/>
-      <c r="BI23" s="151"/>
-      <c r="BJ23" s="151"/>
-      <c r="BK23" s="152"/>
+      <c r="C23" s="152"/>
+      <c r="D23" s="152"/>
+      <c r="E23" s="152"/>
+      <c r="F23" s="152"/>
+      <c r="G23" s="152"/>
+      <c r="H23" s="152"/>
+      <c r="I23" s="152"/>
+      <c r="J23" s="152"/>
+      <c r="K23" s="152"/>
+      <c r="L23" s="152"/>
+      <c r="M23" s="152"/>
+      <c r="N23" s="152"/>
+      <c r="O23" s="152"/>
+      <c r="P23" s="152"/>
+      <c r="Q23" s="152"/>
+      <c r="R23" s="152"/>
+      <c r="S23" s="152"/>
+      <c r="T23" s="152"/>
+      <c r="U23" s="152"/>
+      <c r="V23" s="152"/>
+      <c r="W23" s="152"/>
+      <c r="X23" s="152"/>
+      <c r="Y23" s="152"/>
+      <c r="Z23" s="152"/>
+      <c r="AA23" s="152"/>
+      <c r="AB23" s="152"/>
+      <c r="AC23" s="152"/>
+      <c r="AD23" s="152"/>
+      <c r="AE23" s="152"/>
+      <c r="AF23" s="152"/>
+      <c r="AG23" s="152"/>
+      <c r="AH23" s="152"/>
+      <c r="AI23" s="152"/>
+      <c r="AJ23" s="152"/>
+      <c r="AK23" s="152"/>
+      <c r="AL23" s="152"/>
+      <c r="AM23" s="152"/>
+      <c r="AN23" s="152"/>
+      <c r="AO23" s="152"/>
+      <c r="AP23" s="152"/>
+      <c r="AQ23" s="152"/>
+      <c r="AR23" s="152"/>
+      <c r="AS23" s="152"/>
+      <c r="AT23" s="152"/>
+      <c r="AU23" s="152"/>
+      <c r="AV23" s="152"/>
+      <c r="AW23" s="152"/>
+      <c r="AX23" s="152"/>
+      <c r="AY23" s="152"/>
+      <c r="AZ23" s="152"/>
+      <c r="BA23" s="152"/>
+      <c r="BB23" s="152"/>
+      <c r="BC23" s="152"/>
+      <c r="BD23" s="152"/>
+      <c r="BE23" s="152"/>
+      <c r="BF23" s="152"/>
+      <c r="BG23" s="152"/>
+      <c r="BH23" s="152"/>
+      <c r="BI23" s="152"/>
+      <c r="BJ23" s="152"/>
+      <c r="BK23" s="153"/>
     </row>
     <row r="24" spans="2:68" ht="16.7" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B24" s="78" t="s">
@@ -2623,7 +2666,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="84" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="24"/>
@@ -2664,7 +2707,7 @@
         <v>1</v>
       </c>
       <c r="AR25" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AY25" s="74"/>
       <c r="BK25" s="17"/>
@@ -2676,7 +2719,7 @@
         <v>2</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E26" s="24"/>
       <c r="F26" s="24"/>
@@ -2701,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="AR26" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AY26" s="74"/>
       <c r="BK26" s="17"/>
@@ -2713,7 +2756,7 @@
         <v>3</v>
       </c>
       <c r="C27" s="87" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E27" s="24"/>
       <c r="F27" s="24"/>
@@ -2753,7 +2796,7 @@
         <v>3</v>
       </c>
       <c r="AR27" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AU27" s="9"/>
       <c r="AY27" s="9"/>
@@ -2766,7 +2809,7 @@
         <v>4</v>
       </c>
       <c r="C28" s="87" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D28" s="87"/>
       <c r="E28" s="24"/>
@@ -2807,7 +2850,7 @@
         <v>4</v>
       </c>
       <c r="AR28" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AS28" s="11"/>
       <c r="AU28" s="9"/>
@@ -2820,10 +2863,10 @@
     <row r="29" spans="2:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="42"/>
       <c r="C29" s="87" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="87" t="s">
         <v>33</v>
-      </c>
-      <c r="D29" s="87" t="s">
-        <v>34</v>
       </c>
       <c r="E29" s="24"/>
       <c r="F29" s="24"/>
@@ -2861,7 +2904,7 @@
       <c r="AP29" s="31"/>
       <c r="AQ29" s="10"/>
       <c r="AR29" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AS29" s="11"/>
       <c r="AU29" s="9"/>
@@ -2874,10 +2917,10 @@
     <row r="30" spans="2:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="42"/>
       <c r="C30" s="87" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="87" t="s">
         <v>35</v>
-      </c>
-      <c r="D30" s="87" t="s">
-        <v>36</v>
       </c>
       <c r="E30" s="24"/>
       <c r="F30" s="24"/>
@@ -2917,7 +2960,7 @@
         <v>5</v>
       </c>
       <c r="AR30" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AS30" s="11"/>
       <c r="AU30" s="9"/>
@@ -2932,7 +2975,7 @@
         <v>5</v>
       </c>
       <c r="C31" s="88" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D31" s="87"/>
       <c r="E31" s="24"/>
@@ -2971,7 +3014,7 @@
       <c r="AP31" s="31"/>
       <c r="AQ31" s="10"/>
       <c r="AR31" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AS31" s="11"/>
       <c r="AU31" s="9"/>
@@ -2984,7 +3027,7 @@
     <row r="32" spans="2:68" x14ac:dyDescent="0.25">
       <c r="B32" s="42"/>
       <c r="C32" s="88" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D32" s="87"/>
       <c r="E32" s="24"/>
@@ -3025,7 +3068,7 @@
         <v>6</v>
       </c>
       <c r="AR32" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AS32" s="11"/>
       <c r="AU32" s="9"/>
@@ -3036,7 +3079,7 @@
         <v>6</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D33" s="87"/>
       <c r="E33" s="24"/>
@@ -3075,7 +3118,7 @@
       <c r="AP33" s="31"/>
       <c r="AQ33" s="10"/>
       <c r="AR33" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AS33" s="11"/>
       <c r="AU33" s="9"/>
@@ -3084,7 +3127,7 @@
     <row r="34" spans="1:68" x14ac:dyDescent="0.25">
       <c r="B34" s="82"/>
       <c r="C34" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="24"/>
@@ -3168,7 +3211,7 @@
     </row>
     <row r="37" spans="1:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="128" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C37" s="129"/>
       <c r="D37" s="74"/>
@@ -3781,68 +3824,68 @@
     </row>
     <row r="47" spans="1:68" s="30" customFormat="1" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="12"/>
-      <c r="B47" s="155"/>
-      <c r="C47" s="155"/>
-      <c r="D47" s="155"/>
-      <c r="E47" s="155"/>
-      <c r="F47" s="155"/>
-      <c r="G47" s="155"/>
-      <c r="H47" s="155"/>
-      <c r="I47" s="155"/>
-      <c r="J47" s="155"/>
-      <c r="K47" s="155"/>
-      <c r="L47" s="155"/>
-      <c r="M47" s="155"/>
-      <c r="N47" s="155"/>
-      <c r="O47" s="155"/>
-      <c r="P47" s="155"/>
-      <c r="Q47" s="155"/>
-      <c r="R47" s="155"/>
-      <c r="S47" s="155"/>
-      <c r="T47" s="155"/>
-      <c r="U47" s="155"/>
-      <c r="V47" s="155"/>
-      <c r="W47" s="155"/>
-      <c r="X47" s="155"/>
-      <c r="Y47" s="155"/>
-      <c r="Z47" s="155"/>
-      <c r="AA47" s="155"/>
-      <c r="AB47" s="155"/>
-      <c r="AC47" s="155"/>
-      <c r="AD47" s="155"/>
-      <c r="AE47" s="155"/>
-      <c r="AF47" s="155"/>
-      <c r="AG47" s="155"/>
-      <c r="AH47" s="155"/>
-      <c r="AI47" s="155"/>
-      <c r="AJ47" s="155"/>
-      <c r="AK47" s="155"/>
-      <c r="AL47" s="155"/>
-      <c r="AM47" s="155"/>
-      <c r="AN47" s="155"/>
-      <c r="AO47" s="155"/>
-      <c r="AP47" s="155"/>
-      <c r="AQ47" s="155"/>
-      <c r="AR47" s="155"/>
-      <c r="AS47" s="155"/>
-      <c r="AT47" s="155"/>
-      <c r="AU47" s="155"/>
-      <c r="AV47" s="155"/>
-      <c r="AW47" s="155"/>
-      <c r="AX47" s="155"/>
-      <c r="AY47" s="155"/>
-      <c r="AZ47" s="155"/>
-      <c r="BA47" s="155"/>
-      <c r="BB47" s="155"/>
-      <c r="BC47" s="155"/>
-      <c r="BD47" s="155"/>
-      <c r="BE47" s="155"/>
-      <c r="BF47" s="155"/>
-      <c r="BG47" s="155"/>
-      <c r="BH47" s="155"/>
-      <c r="BI47" s="155"/>
-      <c r="BJ47" s="155"/>
-      <c r="BK47" s="155"/>
+      <c r="B47" s="175"/>
+      <c r="C47" s="175"/>
+      <c r="D47" s="175"/>
+      <c r="E47" s="175"/>
+      <c r="F47" s="175"/>
+      <c r="G47" s="175"/>
+      <c r="H47" s="175"/>
+      <c r="I47" s="175"/>
+      <c r="J47" s="175"/>
+      <c r="K47" s="175"/>
+      <c r="L47" s="175"/>
+      <c r="M47" s="175"/>
+      <c r="N47" s="175"/>
+      <c r="O47" s="175"/>
+      <c r="P47" s="175"/>
+      <c r="Q47" s="175"/>
+      <c r="R47" s="175"/>
+      <c r="S47" s="175"/>
+      <c r="T47" s="175"/>
+      <c r="U47" s="175"/>
+      <c r="V47" s="175"/>
+      <c r="W47" s="175"/>
+      <c r="X47" s="175"/>
+      <c r="Y47" s="175"/>
+      <c r="Z47" s="175"/>
+      <c r="AA47" s="175"/>
+      <c r="AB47" s="175"/>
+      <c r="AC47" s="175"/>
+      <c r="AD47" s="175"/>
+      <c r="AE47" s="175"/>
+      <c r="AF47" s="175"/>
+      <c r="AG47" s="175"/>
+      <c r="AH47" s="175"/>
+      <c r="AI47" s="175"/>
+      <c r="AJ47" s="175"/>
+      <c r="AK47" s="175"/>
+      <c r="AL47" s="175"/>
+      <c r="AM47" s="175"/>
+      <c r="AN47" s="175"/>
+      <c r="AO47" s="175"/>
+      <c r="AP47" s="175"/>
+      <c r="AQ47" s="175"/>
+      <c r="AR47" s="175"/>
+      <c r="AS47" s="175"/>
+      <c r="AT47" s="175"/>
+      <c r="AU47" s="175"/>
+      <c r="AV47" s="175"/>
+      <c r="AW47" s="175"/>
+      <c r="AX47" s="175"/>
+      <c r="AY47" s="175"/>
+      <c r="AZ47" s="175"/>
+      <c r="BA47" s="175"/>
+      <c r="BB47" s="175"/>
+      <c r="BC47" s="175"/>
+      <c r="BD47" s="175"/>
+      <c r="BE47" s="175"/>
+      <c r="BF47" s="175"/>
+      <c r="BG47" s="175"/>
+      <c r="BH47" s="175"/>
+      <c r="BI47" s="175"/>
+      <c r="BJ47" s="175"/>
+      <c r="BK47" s="175"/>
       <c r="BL47" s="12"/>
     </row>
     <row r="48" spans="1:68" ht="21.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
@@ -3857,37 +3900,37 @@
       <c r="J48" s="50"/>
       <c r="K48" s="50"/>
       <c r="L48" s="51"/>
-      <c r="M48" s="168" t="s">
+      <c r="M48" s="163" t="s">
         <v>0</v>
       </c>
-      <c r="N48" s="169"/>
-      <c r="O48" s="169"/>
-      <c r="P48" s="169"/>
-      <c r="Q48" s="169"/>
-      <c r="R48" s="169"/>
-      <c r="S48" s="169"/>
-      <c r="T48" s="169"/>
-      <c r="U48" s="169"/>
-      <c r="V48" s="169"/>
-      <c r="W48" s="169"/>
-      <c r="X48" s="169"/>
-      <c r="Y48" s="169"/>
-      <c r="Z48" s="169"/>
-      <c r="AA48" s="169"/>
-      <c r="AB48" s="169"/>
-      <c r="AC48" s="169"/>
-      <c r="AD48" s="169"/>
-      <c r="AE48" s="169"/>
-      <c r="AF48" s="169"/>
-      <c r="AG48" s="169"/>
-      <c r="AH48" s="169"/>
-      <c r="AI48" s="169"/>
-      <c r="AJ48" s="169"/>
-      <c r="AK48" s="169"/>
-      <c r="AL48" s="169"/>
-      <c r="AM48" s="169"/>
-      <c r="AN48" s="169"/>
-      <c r="AO48" s="170"/>
+      <c r="N48" s="164"/>
+      <c r="O48" s="164"/>
+      <c r="P48" s="164"/>
+      <c r="Q48" s="164"/>
+      <c r="R48" s="164"/>
+      <c r="S48" s="164"/>
+      <c r="T48" s="164"/>
+      <c r="U48" s="164"/>
+      <c r="V48" s="164"/>
+      <c r="W48" s="164"/>
+      <c r="X48" s="164"/>
+      <c r="Y48" s="164"/>
+      <c r="Z48" s="164"/>
+      <c r="AA48" s="164"/>
+      <c r="AB48" s="164"/>
+      <c r="AC48" s="164"/>
+      <c r="AD48" s="164"/>
+      <c r="AE48" s="164"/>
+      <c r="AF48" s="164"/>
+      <c r="AG48" s="164"/>
+      <c r="AH48" s="164"/>
+      <c r="AI48" s="164"/>
+      <c r="AJ48" s="164"/>
+      <c r="AK48" s="164"/>
+      <c r="AL48" s="164"/>
+      <c r="AM48" s="164"/>
+      <c r="AN48" s="164"/>
+      <c r="AO48" s="165"/>
       <c r="AP48" s="140"/>
       <c r="AQ48" s="52" t="str">
         <f>$AQ$2</f>
@@ -3924,35 +3967,35 @@
     <row r="49" spans="2:87" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="31"/>
       <c r="L49" s="17"/>
-      <c r="M49" s="171"/>
-      <c r="N49" s="172"/>
-      <c r="O49" s="172"/>
-      <c r="P49" s="172"/>
-      <c r="Q49" s="172"/>
-      <c r="R49" s="172"/>
-      <c r="S49" s="172"/>
-      <c r="T49" s="172"/>
-      <c r="U49" s="172"/>
-      <c r="V49" s="172"/>
-      <c r="W49" s="172"/>
-      <c r="X49" s="172"/>
-      <c r="Y49" s="172"/>
-      <c r="Z49" s="172"/>
-      <c r="AA49" s="172"/>
-      <c r="AB49" s="172"/>
-      <c r="AC49" s="172"/>
-      <c r="AD49" s="172"/>
-      <c r="AE49" s="172"/>
-      <c r="AF49" s="172"/>
-      <c r="AG49" s="172"/>
-      <c r="AH49" s="172"/>
-      <c r="AI49" s="172"/>
-      <c r="AJ49" s="172"/>
-      <c r="AK49" s="172"/>
-      <c r="AL49" s="172"/>
-      <c r="AM49" s="172"/>
-      <c r="AN49" s="172"/>
-      <c r="AO49" s="173"/>
+      <c r="M49" s="166"/>
+      <c r="N49" s="167"/>
+      <c r="O49" s="167"/>
+      <c r="P49" s="167"/>
+      <c r="Q49" s="167"/>
+      <c r="R49" s="167"/>
+      <c r="S49" s="167"/>
+      <c r="T49" s="167"/>
+      <c r="U49" s="167"/>
+      <c r="V49" s="167"/>
+      <c r="W49" s="167"/>
+      <c r="X49" s="167"/>
+      <c r="Y49" s="167"/>
+      <c r="Z49" s="167"/>
+      <c r="AA49" s="167"/>
+      <c r="AB49" s="167"/>
+      <c r="AC49" s="167"/>
+      <c r="AD49" s="167"/>
+      <c r="AE49" s="167"/>
+      <c r="AF49" s="167"/>
+      <c r="AG49" s="167"/>
+      <c r="AH49" s="167"/>
+      <c r="AI49" s="167"/>
+      <c r="AJ49" s="167"/>
+      <c r="AK49" s="167"/>
+      <c r="AL49" s="167"/>
+      <c r="AM49" s="167"/>
+      <c r="AN49" s="167"/>
+      <c r="AO49" s="168"/>
       <c r="AP49" s="141"/>
       <c r="AQ49" s="30" t="str">
         <f>$AQ$4</f>
@@ -3988,35 +4031,35 @@
     <row r="50" spans="2:87" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="31"/>
       <c r="L50" s="17"/>
-      <c r="M50" s="171"/>
-      <c r="N50" s="172"/>
-      <c r="O50" s="172"/>
-      <c r="P50" s="172"/>
-      <c r="Q50" s="172"/>
-      <c r="R50" s="172"/>
-      <c r="S50" s="172"/>
-      <c r="T50" s="172"/>
-      <c r="U50" s="172"/>
-      <c r="V50" s="172"/>
-      <c r="W50" s="172"/>
-      <c r="X50" s="172"/>
-      <c r="Y50" s="172"/>
-      <c r="Z50" s="172"/>
-      <c r="AA50" s="172"/>
-      <c r="AB50" s="172"/>
-      <c r="AC50" s="172"/>
-      <c r="AD50" s="172"/>
-      <c r="AE50" s="172"/>
-      <c r="AF50" s="172"/>
-      <c r="AG50" s="172"/>
-      <c r="AH50" s="172"/>
-      <c r="AI50" s="172"/>
-      <c r="AJ50" s="172"/>
-      <c r="AK50" s="172"/>
-      <c r="AL50" s="172"/>
-      <c r="AM50" s="172"/>
-      <c r="AN50" s="172"/>
-      <c r="AO50" s="173"/>
+      <c r="M50" s="166"/>
+      <c r="N50" s="167"/>
+      <c r="O50" s="167"/>
+      <c r="P50" s="167"/>
+      <c r="Q50" s="167"/>
+      <c r="R50" s="167"/>
+      <c r="S50" s="167"/>
+      <c r="T50" s="167"/>
+      <c r="U50" s="167"/>
+      <c r="V50" s="167"/>
+      <c r="W50" s="167"/>
+      <c r="X50" s="167"/>
+      <c r="Y50" s="167"/>
+      <c r="Z50" s="167"/>
+      <c r="AA50" s="167"/>
+      <c r="AB50" s="167"/>
+      <c r="AC50" s="167"/>
+      <c r="AD50" s="167"/>
+      <c r="AE50" s="167"/>
+      <c r="AF50" s="167"/>
+      <c r="AG50" s="167"/>
+      <c r="AH50" s="167"/>
+      <c r="AI50" s="167"/>
+      <c r="AJ50" s="167"/>
+      <c r="AK50" s="167"/>
+      <c r="AL50" s="167"/>
+      <c r="AM50" s="167"/>
+      <c r="AN50" s="167"/>
+      <c r="AO50" s="168"/>
       <c r="AP50" s="142"/>
       <c r="AQ50" s="55"/>
       <c r="AR50" s="55"/>
@@ -4053,35 +4096,35 @@
       <c r="J51" s="28"/>
       <c r="K51" s="28"/>
       <c r="L51" s="36"/>
-      <c r="M51" s="174"/>
-      <c r="N51" s="175"/>
-      <c r="O51" s="175"/>
-      <c r="P51" s="175"/>
-      <c r="Q51" s="175"/>
-      <c r="R51" s="175"/>
-      <c r="S51" s="175"/>
-      <c r="T51" s="175"/>
-      <c r="U51" s="175"/>
-      <c r="V51" s="175"/>
-      <c r="W51" s="175"/>
-      <c r="X51" s="175"/>
-      <c r="Y51" s="175"/>
-      <c r="Z51" s="175"/>
-      <c r="AA51" s="175"/>
-      <c r="AB51" s="175"/>
-      <c r="AC51" s="175"/>
-      <c r="AD51" s="175"/>
-      <c r="AE51" s="175"/>
-      <c r="AF51" s="175"/>
-      <c r="AG51" s="175"/>
-      <c r="AH51" s="175"/>
-      <c r="AI51" s="175"/>
-      <c r="AJ51" s="175"/>
-      <c r="AK51" s="175"/>
-      <c r="AL51" s="175"/>
-      <c r="AM51" s="175"/>
-      <c r="AN51" s="175"/>
-      <c r="AO51" s="176"/>
+      <c r="M51" s="169"/>
+      <c r="N51" s="170"/>
+      <c r="O51" s="170"/>
+      <c r="P51" s="170"/>
+      <c r="Q51" s="170"/>
+      <c r="R51" s="170"/>
+      <c r="S51" s="170"/>
+      <c r="T51" s="170"/>
+      <c r="U51" s="170"/>
+      <c r="V51" s="170"/>
+      <c r="W51" s="170"/>
+      <c r="X51" s="170"/>
+      <c r="Y51" s="170"/>
+      <c r="Z51" s="170"/>
+      <c r="AA51" s="170"/>
+      <c r="AB51" s="170"/>
+      <c r="AC51" s="170"/>
+      <c r="AD51" s="170"/>
+      <c r="AE51" s="170"/>
+      <c r="AF51" s="170"/>
+      <c r="AG51" s="170"/>
+      <c r="AH51" s="170"/>
+      <c r="AI51" s="170"/>
+      <c r="AJ51" s="170"/>
+      <c r="AK51" s="170"/>
+      <c r="AL51" s="170"/>
+      <c r="AM51" s="170"/>
+      <c r="AN51" s="170"/>
+      <c r="AO51" s="171"/>
       <c r="AP51" s="143"/>
       <c r="AQ51" s="58" t="str">
         <f>$AQ$5</f>
@@ -4184,74 +4227,74 @@
       <c r="BP53" s="9"/>
     </row>
     <row r="54" spans="2:87" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="156" t="s">
+      <c r="B54" s="176" t="s">
         <v>16</v>
       </c>
-      <c r="C54" s="157"/>
-      <c r="D54" s="157"/>
-      <c r="E54" s="157"/>
-      <c r="F54" s="157"/>
-      <c r="G54" s="157"/>
-      <c r="H54" s="157"/>
-      <c r="I54" s="157"/>
-      <c r="J54" s="157"/>
-      <c r="K54" s="157"/>
-      <c r="L54" s="157"/>
-      <c r="M54" s="157"/>
-      <c r="N54" s="157"/>
-      <c r="O54" s="157"/>
-      <c r="P54" s="157"/>
-      <c r="Q54" s="157"/>
-      <c r="R54" s="157"/>
-      <c r="S54" s="157"/>
-      <c r="T54" s="158"/>
+      <c r="C54" s="177"/>
+      <c r="D54" s="177"/>
+      <c r="E54" s="177"/>
+      <c r="F54" s="177"/>
+      <c r="G54" s="177"/>
+      <c r="H54" s="177"/>
+      <c r="I54" s="177"/>
+      <c r="J54" s="177"/>
+      <c r="K54" s="177"/>
+      <c r="L54" s="177"/>
+      <c r="M54" s="177"/>
+      <c r="N54" s="177"/>
+      <c r="O54" s="177"/>
+      <c r="P54" s="177"/>
+      <c r="Q54" s="177"/>
+      <c r="R54" s="177"/>
+      <c r="S54" s="177"/>
+      <c r="T54" s="178"/>
       <c r="U54" s="30"/>
-      <c r="V54" s="156" t="s">
+      <c r="V54" s="176" t="s">
         <v>17</v>
       </c>
-      <c r="W54" s="157"/>
-      <c r="X54" s="157"/>
-      <c r="Y54" s="157"/>
-      <c r="Z54" s="157"/>
-      <c r="AA54" s="157"/>
-      <c r="AB54" s="157"/>
-      <c r="AC54" s="157"/>
-      <c r="AD54" s="157"/>
-      <c r="AE54" s="157"/>
-      <c r="AF54" s="157"/>
-      <c r="AG54" s="157"/>
-      <c r="AH54" s="157"/>
-      <c r="AI54" s="157"/>
-      <c r="AJ54" s="157"/>
-      <c r="AK54" s="157"/>
-      <c r="AL54" s="157"/>
-      <c r="AM54" s="157"/>
-      <c r="AN54" s="157"/>
-      <c r="AO54" s="158"/>
+      <c r="W54" s="177"/>
+      <c r="X54" s="177"/>
+      <c r="Y54" s="177"/>
+      <c r="Z54" s="177"/>
+      <c r="AA54" s="177"/>
+      <c r="AB54" s="177"/>
+      <c r="AC54" s="177"/>
+      <c r="AD54" s="177"/>
+      <c r="AE54" s="177"/>
+      <c r="AF54" s="177"/>
+      <c r="AG54" s="177"/>
+      <c r="AH54" s="177"/>
+      <c r="AI54" s="177"/>
+      <c r="AJ54" s="177"/>
+      <c r="AK54" s="177"/>
+      <c r="AL54" s="177"/>
+      <c r="AM54" s="177"/>
+      <c r="AN54" s="177"/>
+      <c r="AO54" s="178"/>
       <c r="AP54" s="30"/>
-      <c r="AQ54" s="156" t="s">
+      <c r="AQ54" s="176" t="s">
         <v>18</v>
       </c>
-      <c r="AR54" s="157"/>
-      <c r="AS54" s="157"/>
-      <c r="AT54" s="157"/>
-      <c r="AU54" s="157"/>
-      <c r="AV54" s="157"/>
-      <c r="AW54" s="157"/>
-      <c r="AX54" s="157"/>
-      <c r="AY54" s="157"/>
-      <c r="AZ54" s="157"/>
-      <c r="BA54" s="157"/>
-      <c r="BB54" s="157"/>
-      <c r="BC54" s="157"/>
-      <c r="BD54" s="157"/>
-      <c r="BE54" s="157"/>
-      <c r="BF54" s="157"/>
-      <c r="BG54" s="157"/>
-      <c r="BH54" s="157"/>
-      <c r="BI54" s="157"/>
-      <c r="BJ54" s="157"/>
-      <c r="BK54" s="158"/>
+      <c r="AR54" s="177"/>
+      <c r="AS54" s="177"/>
+      <c r="AT54" s="177"/>
+      <c r="AU54" s="177"/>
+      <c r="AV54" s="177"/>
+      <c r="AW54" s="177"/>
+      <c r="AX54" s="177"/>
+      <c r="AY54" s="177"/>
+      <c r="AZ54" s="177"/>
+      <c r="BA54" s="177"/>
+      <c r="BB54" s="177"/>
+      <c r="BC54" s="177"/>
+      <c r="BD54" s="177"/>
+      <c r="BE54" s="177"/>
+      <c r="BF54" s="177"/>
+      <c r="BG54" s="177"/>
+      <c r="BH54" s="177"/>
+      <c r="BI54" s="177"/>
+      <c r="BJ54" s="177"/>
+      <c r="BK54" s="178"/>
       <c r="BN54" s="9"/>
       <c r="BO54" s="2"/>
       <c r="BP54" s="9"/>
@@ -4298,31 +4341,31 @@
       <c r="BH55" s="14"/>
       <c r="BI55" s="14"/>
       <c r="BK55" s="17"/>
-      <c r="BO55" s="177"/>
-      <c r="BP55" s="177"/>
-      <c r="BQ55" s="177"/>
-      <c r="BR55" s="177"/>
-      <c r="BS55" s="177"/>
-      <c r="BT55" s="177"/>
-      <c r="BU55" s="177"/>
-      <c r="BV55" s="177"/>
-      <c r="BW55" s="177"/>
-      <c r="BX55" s="177"/>
-      <c r="BY55" s="177"/>
-      <c r="BZ55" s="177"/>
-      <c r="CA55" s="177"/>
-      <c r="CB55" s="177"/>
-      <c r="CC55" s="177"/>
-      <c r="CD55" s="177"/>
-      <c r="CE55" s="177"/>
-      <c r="CF55" s="177"/>
-      <c r="CG55" s="177"/>
-      <c r="CH55" s="177"/>
-      <c r="CI55" s="177"/>
+      <c r="BO55" s="172"/>
+      <c r="BP55" s="172"/>
+      <c r="BQ55" s="172"/>
+      <c r="BR55" s="172"/>
+      <c r="BS55" s="172"/>
+      <c r="BT55" s="172"/>
+      <c r="BU55" s="172"/>
+      <c r="BV55" s="172"/>
+      <c r="BW55" s="172"/>
+      <c r="BX55" s="172"/>
+      <c r="BY55" s="172"/>
+      <c r="BZ55" s="172"/>
+      <c r="CA55" s="172"/>
+      <c r="CB55" s="172"/>
+      <c r="CC55" s="172"/>
+      <c r="CD55" s="172"/>
+      <c r="CE55" s="172"/>
+      <c r="CF55" s="172"/>
+      <c r="CG55" s="172"/>
+      <c r="CH55" s="172"/>
+      <c r="CI55" s="172"/>
     </row>
     <row r="56" spans="2:87" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="127" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C56" s="33"/>
       <c r="D56" s="11"/>
@@ -4344,7 +4387,7 @@
         <v>1</v>
       </c>
       <c r="W56" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="X56" s="5"/>
       <c r="AO56" s="17"/>
@@ -4503,7 +4546,7 @@
       <c r="AO59" s="17"/>
       <c r="AQ59" s="10"/>
       <c r="AR59" s="18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AS59" s="14"/>
       <c r="AT59" s="14"/>
@@ -4692,7 +4735,7 @@
         <v>4</v>
       </c>
       <c r="AR63" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AT63" s="20"/>
       <c r="AU63" s="20"/>
@@ -4838,23 +4881,23 @@
       <c r="BI66" s="20"/>
       <c r="BK66" s="17"/>
       <c r="BO66" s="30"/>
-      <c r="BP66" s="177"/>
-      <c r="BQ66" s="177"/>
-      <c r="BR66" s="177"/>
-      <c r="BS66" s="177"/>
-      <c r="BT66" s="177"/>
-      <c r="BU66" s="177"/>
-      <c r="BV66" s="177"/>
-      <c r="BW66" s="177"/>
-      <c r="BX66" s="177"/>
-      <c r="BY66" s="177"/>
-      <c r="BZ66" s="177"/>
-      <c r="CA66" s="177"/>
-      <c r="CB66" s="177"/>
-      <c r="CC66" s="177"/>
-      <c r="CD66" s="177"/>
-      <c r="CE66" s="177"/>
-      <c r="CF66" s="177"/>
+      <c r="BP66" s="172"/>
+      <c r="BQ66" s="172"/>
+      <c r="BR66" s="172"/>
+      <c r="BS66" s="172"/>
+      <c r="BT66" s="172"/>
+      <c r="BU66" s="172"/>
+      <c r="BV66" s="172"/>
+      <c r="BW66" s="172"/>
+      <c r="BX66" s="172"/>
+      <c r="BY66" s="172"/>
+      <c r="BZ66" s="172"/>
+      <c r="CA66" s="172"/>
+      <c r="CB66" s="172"/>
+      <c r="CC66" s="172"/>
+      <c r="CD66" s="172"/>
+      <c r="CE66" s="172"/>
+      <c r="CF66" s="172"/>
     </row>
     <row r="67" spans="2:84" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B67" s="42"/>
@@ -4952,28 +4995,28 @@
       <c r="R69" s="24"/>
       <c r="S69" s="24"/>
       <c r="T69" s="108"/>
-      <c r="V69" s="150" t="s">
+      <c r="V69" s="151" t="s">
         <v>25</v>
       </c>
-      <c r="W69" s="151"/>
-      <c r="X69" s="151"/>
-      <c r="Y69" s="151"/>
-      <c r="Z69" s="151"/>
-      <c r="AA69" s="151"/>
-      <c r="AB69" s="151"/>
-      <c r="AC69" s="151"/>
-      <c r="AD69" s="151"/>
-      <c r="AE69" s="151"/>
-      <c r="AF69" s="151"/>
-      <c r="AG69" s="151"/>
-      <c r="AH69" s="151"/>
-      <c r="AI69" s="151"/>
-      <c r="AJ69" s="151"/>
-      <c r="AK69" s="151"/>
-      <c r="AL69" s="151"/>
-      <c r="AM69" s="151"/>
-      <c r="AN69" s="151"/>
-      <c r="AO69" s="152"/>
+      <c r="W69" s="152"/>
+      <c r="X69" s="152"/>
+      <c r="Y69" s="152"/>
+      <c r="Z69" s="152"/>
+      <c r="AA69" s="152"/>
+      <c r="AB69" s="152"/>
+      <c r="AC69" s="152"/>
+      <c r="AD69" s="152"/>
+      <c r="AE69" s="152"/>
+      <c r="AF69" s="152"/>
+      <c r="AG69" s="152"/>
+      <c r="AH69" s="152"/>
+      <c r="AI69" s="152"/>
+      <c r="AJ69" s="152"/>
+      <c r="AK69" s="152"/>
+      <c r="AL69" s="152"/>
+      <c r="AM69" s="152"/>
+      <c r="AN69" s="152"/>
+      <c r="AO69" s="153"/>
       <c r="AP69" s="75"/>
       <c r="AS69" s="20"/>
       <c r="AT69" s="20"/>
@@ -5326,24 +5369,24 @@
       <c r="AO78" s="17"/>
       <c r="AP78" s="17"/>
       <c r="BK78" s="17"/>
-      <c r="BO78" s="177"/>
-      <c r="BP78" s="177"/>
-      <c r="BQ78" s="177"/>
-      <c r="BR78" s="177"/>
-      <c r="BS78" s="177"/>
-      <c r="BT78" s="177"/>
-      <c r="BU78" s="177"/>
-      <c r="BV78" s="177"/>
-      <c r="BW78" s="177"/>
-      <c r="BX78" s="177"/>
-      <c r="BY78" s="177"/>
-      <c r="BZ78" s="177"/>
-      <c r="CA78" s="177"/>
-      <c r="CB78" s="177"/>
-      <c r="CC78" s="177"/>
-      <c r="CD78" s="177"/>
-      <c r="CE78" s="177"/>
-      <c r="CF78" s="177"/>
+      <c r="BO78" s="172"/>
+      <c r="BP78" s="172"/>
+      <c r="BQ78" s="172"/>
+      <c r="BR78" s="172"/>
+      <c r="BS78" s="172"/>
+      <c r="BT78" s="172"/>
+      <c r="BU78" s="172"/>
+      <c r="BV78" s="172"/>
+      <c r="BW78" s="172"/>
+      <c r="BX78" s="172"/>
+      <c r="BY78" s="172"/>
+      <c r="BZ78" s="172"/>
+      <c r="CA78" s="172"/>
+      <c r="CB78" s="172"/>
+      <c r="CC78" s="172"/>
+      <c r="CD78" s="172"/>
+      <c r="CE78" s="172"/>
+      <c r="CF78" s="172"/>
     </row>
     <row r="79" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B79" s="31"/>
@@ -5388,93 +5431,93 @@
       <c r="BK83" s="36"/>
     </row>
     <row r="84" spans="2:63" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B84" s="150" t="s">
+      <c r="B84" s="151" t="s">
         <v>26</v>
       </c>
-      <c r="C84" s="151"/>
-      <c r="D84" s="151"/>
-      <c r="E84" s="151"/>
-      <c r="F84" s="151"/>
-      <c r="G84" s="151"/>
-      <c r="H84" s="151"/>
-      <c r="I84" s="151"/>
-      <c r="J84" s="151"/>
-      <c r="K84" s="151"/>
-      <c r="L84" s="151"/>
-      <c r="M84" s="151"/>
-      <c r="N84" s="151"/>
-      <c r="O84" s="151"/>
-      <c r="P84" s="151"/>
-      <c r="Q84" s="151"/>
-      <c r="R84" s="151"/>
-      <c r="S84" s="151"/>
-      <c r="T84" s="151"/>
-      <c r="U84" s="151"/>
-      <c r="V84" s="151"/>
-      <c r="W84" s="151"/>
-      <c r="X84" s="151"/>
-      <c r="Y84" s="151"/>
-      <c r="Z84" s="151"/>
-      <c r="AA84" s="151"/>
-      <c r="AB84" s="151"/>
-      <c r="AC84" s="151"/>
-      <c r="AD84" s="151"/>
-      <c r="AE84" s="151"/>
-      <c r="AF84" s="151"/>
-      <c r="AG84" s="151"/>
-      <c r="AH84" s="151"/>
-      <c r="AI84" s="151"/>
-      <c r="AJ84" s="151"/>
-      <c r="AK84" s="151"/>
-      <c r="AL84" s="151"/>
-      <c r="AM84" s="151"/>
-      <c r="AN84" s="151"/>
-      <c r="AO84" s="151"/>
-      <c r="AP84" s="151"/>
-      <c r="AQ84" s="151"/>
-      <c r="AR84" s="151"/>
-      <c r="AS84" s="151"/>
-      <c r="AT84" s="151"/>
-      <c r="AU84" s="151"/>
-      <c r="AV84" s="151"/>
-      <c r="AW84" s="151"/>
-      <c r="AX84" s="151"/>
-      <c r="AY84" s="151"/>
-      <c r="AZ84" s="151"/>
-      <c r="BA84" s="151"/>
-      <c r="BB84" s="151"/>
-      <c r="BC84" s="151"/>
-      <c r="BD84" s="151"/>
-      <c r="BE84" s="151"/>
-      <c r="BF84" s="151"/>
-      <c r="BG84" s="151"/>
-      <c r="BH84" s="151"/>
-      <c r="BI84" s="151"/>
-      <c r="BJ84" s="151"/>
-      <c r="BK84" s="152"/>
+      <c r="C84" s="152"/>
+      <c r="D84" s="152"/>
+      <c r="E84" s="152"/>
+      <c r="F84" s="152"/>
+      <c r="G84" s="152"/>
+      <c r="H84" s="152"/>
+      <c r="I84" s="152"/>
+      <c r="J84" s="152"/>
+      <c r="K84" s="152"/>
+      <c r="L84" s="152"/>
+      <c r="M84" s="152"/>
+      <c r="N84" s="152"/>
+      <c r="O84" s="152"/>
+      <c r="P84" s="152"/>
+      <c r="Q84" s="152"/>
+      <c r="R84" s="152"/>
+      <c r="S84" s="152"/>
+      <c r="T84" s="152"/>
+      <c r="U84" s="152"/>
+      <c r="V84" s="152"/>
+      <c r="W84" s="152"/>
+      <c r="X84" s="152"/>
+      <c r="Y84" s="152"/>
+      <c r="Z84" s="152"/>
+      <c r="AA84" s="152"/>
+      <c r="AB84" s="152"/>
+      <c r="AC84" s="152"/>
+      <c r="AD84" s="152"/>
+      <c r="AE84" s="152"/>
+      <c r="AF84" s="152"/>
+      <c r="AG84" s="152"/>
+      <c r="AH84" s="152"/>
+      <c r="AI84" s="152"/>
+      <c r="AJ84" s="152"/>
+      <c r="AK84" s="152"/>
+      <c r="AL84" s="152"/>
+      <c r="AM84" s="152"/>
+      <c r="AN84" s="152"/>
+      <c r="AO84" s="152"/>
+      <c r="AP84" s="152"/>
+      <c r="AQ84" s="152"/>
+      <c r="AR84" s="152"/>
+      <c r="AS84" s="152"/>
+      <c r="AT84" s="152"/>
+      <c r="AU84" s="152"/>
+      <c r="AV84" s="152"/>
+      <c r="AW84" s="152"/>
+      <c r="AX84" s="152"/>
+      <c r="AY84" s="152"/>
+      <c r="AZ84" s="152"/>
+      <c r="BA84" s="152"/>
+      <c r="BB84" s="152"/>
+      <c r="BC84" s="152"/>
+      <c r="BD84" s="152"/>
+      <c r="BE84" s="152"/>
+      <c r="BF84" s="152"/>
+      <c r="BG84" s="152"/>
+      <c r="BH84" s="152"/>
+      <c r="BI84" s="152"/>
+      <c r="BJ84" s="152"/>
+      <c r="BK84" s="153"/>
     </row>
     <row r="85" spans="2:63" ht="13.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="153" t="s">
+      <c r="B85" s="173" t="s">
         <v>27</v>
       </c>
-      <c r="C85" s="154"/>
-      <c r="D85" s="154"/>
-      <c r="E85" s="154"/>
-      <c r="F85" s="154"/>
-      <c r="G85" s="154"/>
-      <c r="H85" s="154"/>
-      <c r="I85" s="154"/>
-      <c r="J85" s="154"/>
-      <c r="K85" s="154"/>
-      <c r="L85" s="154"/>
-      <c r="M85" s="154"/>
-      <c r="N85" s="154"/>
-      <c r="O85" s="154"/>
-      <c r="P85" s="154"/>
-      <c r="Q85" s="154"/>
-      <c r="R85" s="154"/>
-      <c r="S85" s="154"/>
-      <c r="T85" s="154"/>
+      <c r="C85" s="174"/>
+      <c r="D85" s="174"/>
+      <c r="E85" s="174"/>
+      <c r="F85" s="174"/>
+      <c r="G85" s="174"/>
+      <c r="H85" s="174"/>
+      <c r="I85" s="174"/>
+      <c r="J85" s="174"/>
+      <c r="K85" s="174"/>
+      <c r="L85" s="174"/>
+      <c r="M85" s="174"/>
+      <c r="N85" s="174"/>
+      <c r="O85" s="174"/>
+      <c r="P85" s="174"/>
+      <c r="Q85" s="174"/>
+      <c r="R85" s="174"/>
+      <c r="S85" s="174"/>
+      <c r="T85" s="174"/>
       <c r="U85" s="50"/>
       <c r="V85" s="114" t="s">
         <v>28</v>
@@ -5506,18 +5549,18 @@
       <c r="S86" s="24"/>
       <c r="T86" s="24"/>
       <c r="V86" s="24" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="W86" s="24"/>
       <c r="AQ86" s="116" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AR86" s="6"/>
       <c r="BK86" s="17"/>
     </row>
     <row r="87" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B87" s="31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D87" s="24"/>
       <c r="E87" s="24"/>
@@ -5543,7 +5586,7 @@
     </row>
     <row r="88" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B88" s="149" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E88" s="24"/>
       <c r="F88" s="24"/>
@@ -5562,14 +5605,12 @@
       <c r="S88" s="24"/>
       <c r="T88" s="24"/>
       <c r="V88" s="44" t="s">
-        <v>69</v>
-      </c>
-      <c r="AQ88" s="146" t="s">
-        <v>68</v>
-      </c>
-      <c r="AR88" s="125" t="s">
-        <v>54</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="AQ88" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="AR88" s="125"/>
       <c r="BK88" s="17"/>
     </row>
     <row r="89" spans="2:63" x14ac:dyDescent="0.25">
@@ -5594,12 +5635,8 @@
       <c r="T89" s="24"/>
       <c r="V89" s="146"/>
       <c r="W89" s="144"/>
-      <c r="AQ89" s="146" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR89" s="125" t="s">
-        <v>54</v>
-      </c>
+      <c r="AQ89" s="33"/>
+      <c r="AR89" s="125"/>
       <c r="BK89" s="17"/>
     </row>
     <row r="90" spans="2:63" x14ac:dyDescent="0.25">
@@ -5624,12 +5661,8 @@
       <c r="T90" s="24"/>
       <c r="V90" s="25"/>
       <c r="W90" s="144"/>
-      <c r="AQ90" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="AR90" s="125" t="s">
-        <v>54</v>
-      </c>
+      <c r="AQ90" s="150"/>
+      <c r="AR90" s="125"/>
       <c r="BK90" s="17"/>
     </row>
     <row r="91" spans="2:63" x14ac:dyDescent="0.25">
@@ -5653,7 +5686,7 @@
       <c r="S91" s="24"/>
       <c r="T91" s="24"/>
       <c r="V91" s="44"/>
-      <c r="AQ91" s="44"/>
+      <c r="AQ91" s="150"/>
       <c r="BK91" s="17"/>
     </row>
     <row r="92" spans="2:63" x14ac:dyDescent="0.25">
@@ -5679,6 +5712,7 @@
       <c r="V92" s="45"/>
       <c r="W92" s="6"/>
       <c r="AP92" s="9"/>
+      <c r="AQ92" s="34"/>
       <c r="BK92" s="17"/>
     </row>
     <row r="93" spans="2:63" x14ac:dyDescent="0.25">
@@ -5819,6 +5853,14 @@
     <row r="98" spans="43:43" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B84:BK84"/>
+    <mergeCell ref="B85:T85"/>
+    <mergeCell ref="B23:BK23"/>
+    <mergeCell ref="B47:BK47"/>
+    <mergeCell ref="B54:T54"/>
+    <mergeCell ref="V54:AO54"/>
+    <mergeCell ref="AQ54:BK54"/>
+    <mergeCell ref="V69:AO69"/>
     <mergeCell ref="AQ8:BK8"/>
     <mergeCell ref="X9:AO11"/>
     <mergeCell ref="M2:AO5"/>
@@ -5829,14 +5871,6 @@
     <mergeCell ref="X12:AO12"/>
     <mergeCell ref="B8:W8"/>
     <mergeCell ref="X8:AO8"/>
-    <mergeCell ref="B84:BK84"/>
-    <mergeCell ref="B85:T85"/>
-    <mergeCell ref="B23:BK23"/>
-    <mergeCell ref="B47:BK47"/>
-    <mergeCell ref="B54:T54"/>
-    <mergeCell ref="V54:AO54"/>
-    <mergeCell ref="AQ54:BK54"/>
-    <mergeCell ref="V69:AO69"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0.19685039370078741" header="3.937007874015748E-2" footer="0.23622047244094491"/>
